--- a/notebook/locations.xlsx
+++ b/notebook/locations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T122"/>
+  <dimension ref="A1:V176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,95 +424,105 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>bag_of_words</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>super_region</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>www.geonames.org</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>www.wikidata.org</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>www.giessen.de</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>gedenkbuch.saarbruecken.de</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>tinyurl.com</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>www.facebook.com</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>en.wikipedia.org</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>archiv.schillerschule.de</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>it.wikipedia.org</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>www.alte-zigarrenfabrik.com</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>www.museum.de</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>www.myheritage.it</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>www.sommer-archive.com</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>obits.syracuse.com</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>ballweg.store.helloflowers.com</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>de.wikipedia.org</t>
         </is>
@@ -526,10 +536,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>allenstein</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>52.67</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>13.75</t>
         </is>
@@ -543,20 +558,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>argentinien</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sudamerika</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>-34</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>-64</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.geonames.org/3865483</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q414</t>
         </is>
@@ -570,20 +595,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>auschwitz</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>50.03702</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>19.17612</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.geonames.org/7701596</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q663764</t>
         </is>
@@ -597,20 +632,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>australia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>-25</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2077456</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Herbert_A._David</t>
         </is>
@@ -624,15 +664,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>avignon frankreich provence</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>43.95</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>4.81</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>https://gedenkbuch.saarbruecken.de/gedenkbuch/personen_detailseite/person-3855</t>
         </is>
@@ -646,10 +696,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>avignon südfrankreich</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Südfrankreich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>45.17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>5.33</t>
         </is>
@@ -663,35 +723,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>bad könig</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>49.7432</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>9.0075</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2953419</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q379121</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://www.alte-zigarrenfabrik.com/wp-content/uploads/2022/04/Oppenheimer.endgueltige-Fassung.pdf;</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>https://www.museum.de/audioguide/34/39/DE/0;</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>https://www.myheritage.it/names/isaak_oppenheimer</t>
         </is>
@@ -705,20 +770,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>bahnhof tolouse</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>43.61132</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.45414</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.geonames.org/6301916</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q373449</t>
         </is>
@@ -732,25 +802,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>am bahnhof frankfurt main</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>50.10679</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>8.66317</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Bahnhof,alte_heimat</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.geonames.org/6290300/frankfurt-hauptbahnhof.html</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q1794</t>
         </is>
@@ -764,15 +844,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>belgien</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>50.5</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>3.15</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>reise_zurueck</t>
         </is>
@@ -786,30 +871,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>berlin</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>52.52437</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>13.41053</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>alte_heimat</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2950159</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q64</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Herbert_A._David</t>
         </is>
@@ -823,15 +913,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>berlin brunnenstraße</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>52.53388889</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>13.39833333</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q992834</t>
         </is>
@@ -845,15 +945,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>berlin kolonnenstraße</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>52.4863</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>13.3602</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.geonames.org/maps/google_52.4863_13.3602.html</t>
         </is>
@@ -867,20 +977,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>berlin shoeneberg</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>52.49801</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>13.3443</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2836788</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1183</t>
         </is>
@@ -894,15 +1014,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>berlin siemensstadt</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>52.54053</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>13.26294</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2832373</t>
         </is>
@@ -916,25 +1046,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>bnei brak</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>32.08074</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>34.8338</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.geonames.org/295514</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q152467</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
         </is>
@@ -948,20 +1083,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>brücke kehlstraßburg rheinquerung</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>48.5737</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>7.80194</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Zug,verkehrsmittel</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q1375288</t>
         </is>
@@ -975,20 +1115,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>buchenwald</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>51.02262</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>11.24923</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.geonames.org/8644023</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q152802</t>
         </is>
@@ -1002,15 +1147,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>camp des milles</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>43.502028</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>5.391444</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q481647</t>
         </is>
@@ -1024,15 +1174,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>cornell university</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>42.4491666666667</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>-76.4838888888889</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q49115</t>
         </is>
@@ -1046,15 +1201,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>deutschland</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>5.15</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>reise_zurueck</t>
         </is>
@@ -1068,20 +1228,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>drancy</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>48.92583</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>2.44528</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.geonames.org/12077049</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/w/index.php?search=Drancy&amp;language=en&amp;title=Special%3ASearch&amp;ns0=1</t>
         </is>
@@ -1095,15 +1260,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>encharodl</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>32.55897</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>35.39041</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.geonames.org/295210</t>
         </is>
@@ -1117,10 +1287,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>52.6620403</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>-4.9680331</t>
         </is>
@@ -1134,15 +1309,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>17 crumbach erbacher fränkisch straße</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fränkisch Crumbach</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>49.74</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>8.86</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://www.alte-zigarrenfabrik.com/wp-content/uploads/2022/04/Oppenheimer.endgueltige-Fassung.pdf</t>
         </is>
@@ -1156,20 +1341,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>finsterwalde</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>51.6276</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>13.71515</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://www.geonames.org/6550600</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1183</t>
         </is>
@@ -1183,25 +1373,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>frankfurt</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>50.11552</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>8.68417</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2925533</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q1794</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://archiv.schillerschule.de/images/dokumente/Ehemalige/Schiller-EXtra/schillerextra_11.pdf</t>
         </is>
@@ -1215,25 +1420,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>frankfurt hauptbahnhof main</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>50.10679</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>8.66317</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Zug,verkehrsmittel</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://www.geonames.org/6290300/frankfurt-hauptbahnhof.html</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q165368</t>
         </is>
@@ -1247,10 +1462,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>frankfurt hauptbahnof</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>50.11</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>8.66</t>
         </is>
@@ -1264,25 +1489,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>am frankfurt main</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>50.11035</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>8.67185</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>reise_zurueck,Zug</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://www.geonames.org/6553153/frankfurt-am-main.html</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q1794</t>
         </is>
@@ -1296,20 +1531,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>frankfurtm</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>50.11552</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>8.68417</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2925533</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q1794</t>
         </is>
@@ -1323,15 +1568,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>frankreich</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>45.9966331</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>-2.688227</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-3997</t>
         </is>
@@ -1345,20 +1600,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>crumbach fränkisch</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>49.74611</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>8.85861</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2925507</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q622126</t>
         </is>
@@ -1372,20 +1632,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>48 ghettohaus walltorstraße</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Gießen</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>50.983004</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>11.32848</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>alte_heimat,Ghettohaus</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
         </is>
@@ -1399,25 +1669,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>gießen</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>50.58727</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>8.67554</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>reise_zurueck</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2920512/giessen.html</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q564579</t>
         </is>
@@ -1431,25 +1711,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>11 gießen marktplatz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Gießen</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>50.58727</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>8.67554</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>ort_der_zeit</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2920512</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q564579</t>
         </is>
@@ -1463,25 +1753,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>48 gießen walltorstraße</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Gießen</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>50.983004</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>11.32848</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>alte_heimat,Telephon im Ghettohaus</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2920512</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q564579</t>
         </is>
@@ -1495,20 +1795,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>großbieberau</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>49.80064</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>8.8243</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2916966</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q539579</t>
         </is>
@@ -1522,25 +1827,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>großenlinden</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>50.52785</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>8.662</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>reise_zurueck,Zug</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://www.geonames.org/11974166/grossen-linden.html</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q116016915</t>
         </is>
@@ -1554,10 +1864,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>grundschule volksschule</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>48.04</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>10.67</t>
         </is>
@@ -1571,25 +1886,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>gurs</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>43.27376</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>-0.74031</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>https://www.geonames.org/12494761</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q708638</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>https://it.wikipedia.org/wiki/Memoriale_di_Neckarzimmern</t>
         </is>
@@ -1603,20 +1923,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>göttingen</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>51.53443</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>9.93228</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2918632</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q3033</t>
         </is>
@@ -1630,25 +1955,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>haifa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>32.81303</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>34.99928</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>neue_heimat</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>https://www.geonames.org/294801</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q41621</t>
         </is>
@@ -1662,15 +1992,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>bibliothek haifa universität</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Haifa</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>32.75</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>neue_heimat</t>
         </is>
@@ -1684,20 +2024,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>harwich</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>41.66678</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>-70.07863</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>https://www.geonames.org/4939008</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q990616</t>
         </is>
@@ -1711,20 +2056,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>heidelberg</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>49.40768</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>8.69079</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2907911</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q2966</t>
         </is>
@@ -1738,20 +2088,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>hessen</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>50.55</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2905330</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q1199</t>
         </is>
@@ -1760,883 +2120,1138 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Hilfsperson Michael und Fedora</t>
+          <t>Hoek van Holland</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>38.79</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>-34.23</t>
+          <t>hoek holland van</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>51.9775</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>4.13333</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2754007</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2792592</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Hoek van Holland</t>
+          <t>Homburg (Saar)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>51.9775</t>
+          <t>homburg saar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4.13333</t>
+          <t>Saar</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>49.32637</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2754007</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q2792592</t>
+          <t>7.33867</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2899449</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q7040</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Homburg (Saar)</t>
+          <t>Höchst im Odenwald</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>49.32637</t>
+          <t>höchst im odenwald</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>7.33867</t>
+          <t>Odenwald</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>49.79972</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2899449</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q7040</t>
+          <t>8.99944</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2902951</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q634819</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Höchst im Odenwald</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>49.79972</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>8.99944</t>
+          <t>iowa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>42.00027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2902951</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q634819</t>
+          <t>-93.50049</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/4862182</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1546</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Iowa State University</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>iowa state university</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>Iowa</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>42.00027</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>-93.50049</t>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>42.03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/4862182</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1546</t>
+          <t>-93.65</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Iowa State University</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>42.03</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>-93.65</t>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>30.81</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>34.86</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Israel, Ramatayim</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>israel ramatayim</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>30.81</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>34.86</t>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>32.15355</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>34.88643</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/294951</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q7024558</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Israel, Ramatayim</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>32.15355</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>34.88643</t>
+          <t>italien</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>41.17</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/294951</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q7024558</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
+          <t>reise_zurueck</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Jaffa</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>41.17</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>7.43</t>
+          <t>jaffa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>reise_zurueck</t>
+          <t>32.04</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>34.75</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jaffa</t>
+          <t>Jena</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>32.04</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>34.75</t>
+          <t>jena</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>50.92878</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>11.5899</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2895044</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q3150</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jena</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>50.92878</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>11.5899</t>
+          <t>jordan</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2895044</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q3150</t>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/248816</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Kehl am Rhein</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>am kehl rhein</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>Kehl</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>48.57297</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/248816</t>
+          <t>7.81523</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Zug,verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2891951/kehl.html</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q15979</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kehl am Rhein</t>
+          <t>Kibbuz Ein HaNetziv</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>48.57297</t>
+          <t>ein hanetziv kibbuz</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>7.81523</t>
+          <t>Kibbuz</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Zug,verkehrsmittel</t>
+          <t>32.47037</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2891951/kehl.html</t>
+          <t>35.50242</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q15979</t>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/295211/-en-hanaziv.html</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2095906</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kibbuz Ein HaNetziv</t>
+          <t>Kibbuz Rodges, besteht nicht mehr (in der Nähe von Petah Tikva)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>32.47037</t>
+          <t>besteht der in kibbuz mehr nicht nähe petah rodges tikva von</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>35.50242</t>
+          <t>Kibbuz Rodges</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/295211/-en-hanaziv.html</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q2095906</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kibbuz Rodges, besteht nicht mehr (in der Nähe von Petah Tikva)</t>
+          <t>Kibbuz Tirat Tsvi</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>kibbuz tirat tsvi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>Tirat Tsvi</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>32.42124</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>35.52831</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/293304/tirat-tsvi.html</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q550025</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kibbuz Tirat Tsvi</t>
+          <t>Klein-Linden</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>32.42124</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>35.52831</t>
+          <t>kleinlinden</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>neue_heimat</t>
+          <t>50.55685</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/293304/tirat-tsvi.html</t>
+          <t>8.64712</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q550025</t>
+          <t>reise_zurueck,Zug</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2888549/klein-linden.html</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1571834</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Klein-Linden</t>
+          <t>Kowno, Lituanien</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>50.55685</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>8.64712</t>
+          <t>kowno lituanien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>reise_zurueck,Zug</t>
+          <t>54.90156</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2888549/klein-linden.html</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1571834</t>
+          <t>23.90909</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/598316</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q4115712</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kowno, Lituanien</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>54.90156</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>23.90909</t>
+          <t>leicester</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>52.63</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/598316</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q4115712</t>
+          <t>-1.13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>London</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>52.63</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>-1.13</t>
+          <t>london</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>41.8091</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>12.67942</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/3176589</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q190963</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Löberstraße 20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>41.8091</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>12.67942</t>
+          <t>20 löberstraße</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>50.5805671</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/3176589</t>
+          <t>8.6720277</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q190963</t>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Löberstraße 20</t>
+          <t>Mannheim</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>50.5805671</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>8.6720277</t>
+          <t>mannheim</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>alte_heimat</t>
+          <t>49.4891</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>8.46694</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
+          <t>https://www.geonames.org/2873891</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2119</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://tinyurl.com/33y47jxx</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>https://archiv.schillerschule.de/images/dokumente/Ehemalige/Schiller-EXtra/schillerextra_11.pdf)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>Mannheim Hauptbahnof</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>hauptbahnof mannheim</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>Mannheim</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>49.4891</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>8.46694</t>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>49.48</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2873891</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q2119</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>https://tinyurl.com/33y47jxx</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>https://archiv.schillerschule.de/images/dokumente/Ehemalige/Schiller-EXtra/schillerextra_11.pdf)</t>
+          <t>8.47</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mannheim Hauptbahnof</t>
+          <t>Marktplatz 11, Giessen</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>49.48</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>8.47</t>
+          <t>11 giessen marktplatz</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>50.58727</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>8.67554</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>reise_zurueck,Zug</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Marktplatz 11, Giessen</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>50.58727</t>
+          <t>marseille</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>8.67554</t>
+          <t>Südfrankreich</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>reise_zurueck,Zug</t>
+          <t>43.29695</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>5.38107</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>verkehrsmittel,Schiff</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2995469</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q23482</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1183</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>Marseille (Hafen)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>hafen marseille</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>Marseille</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>43.29695</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>5.38107</t>
-        </is>
-      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>verkehrsmittel,Schiff</t>
+          <t>43.31918</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2995469</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q23482</t>
+          <t>5.35613</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/12196053/grand-port-maritime-de-marseille.html</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1183</t>
+          <t>https://www.wikidata.org/wiki/Q34963701</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Marseille (Hafen)</t>
+          <t>Michelstadt</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>43.31918</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>5.35613</t>
+          <t>michelstadt</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>49.67569</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/12196053/grand-port-maritime-de-marseille.html</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q34963701</t>
+          <t>9.00373</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2871284</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q516517</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Michelstadt</t>
+          <t>Mill Valley</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>49.67569</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>9.00373</t>
+          <t>mill valley</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>37.906111111111</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2871284</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q516517</t>
+          <t>-122.545</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q846413</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Alice_Urbach</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mill Valley</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>37.906111111111</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>-122.545</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q846413</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>https://de.wikipedia.org/wiki/Alice_Urbach</t>
+          <t>montpellier</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>43.61093</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>3.87635</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2992166</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q6441</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Munchen</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>43.61093</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>3.87635</t>
+          <t>munchen</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>48.13743</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2992166</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q6441</t>
+          <t>11.57549</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2867714</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1726</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Munchen</t>
+          <t>Naher Osten</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>48.13743</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>11.57549</t>
+          <t>naher osten</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>51.11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2867714</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1726</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Naher Osten</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>new york</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>40.71427</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-74.00597</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/5128581</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1384</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Niederlande</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>40.71427</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>-74.00597</t>
+          <t>niederlande</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/5128581</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1384</t>
+          <t>reise_zurueck</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Niederlande</t>
+          <t>Nyons (Drôme), Frankreich</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>drôme frankreich nyons</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>Frankreich</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>reise_zurueck</t>
+          <t>44.36</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-3992</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Nyons (Drôme), Frankreich</t>
+          <t>Nyons Südfrankreich</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>nyons südfrankreich</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Südfrankreich</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>44.36</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>5.14</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-3992</t>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Nyons Südfrankreich</t>
+          <t>Nyons, Südfrankreich</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>nyons südfrankreich</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Südfrankreich</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>44.36</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>5.14</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
         </is>
@@ -2645,113 +3260,158 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Nyons, Südfrankreich</t>
+          <t>Nähe Toulouse (Südfrankreich)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>nähe südfrankreich toulouse</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>5.14</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
+          <t>Südfrankreich</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>45.47</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-0.4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Nähe Toulouse (Südfrankreich)</t>
+          <t>Odenwald</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>45.47</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>-0.4</t>
+          <t>odenwald</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>49.61667</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>8.83333</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2858101</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q8359</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Odenwald</t>
+          <t>Odenwald - Fränkisch Crumbach</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>49.61667</t>
+          <t>crumbach fränkisch odenwald</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>8.83333</t>
+          <t>Fränkisch Crumbach</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>49.74611</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2858101</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q8359</t>
+          <t>8.85861</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2925507</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q622126</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Odenwald - Fränkisch Crumbach</t>
+          <t>Orange (Frankreich)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>49.74611</t>
+          <t>frankreich orange</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>8.85861</t>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>44.14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2925507</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q622126</t>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://gedenkbuch.saarbruecken.de/gedenkbuch/personen_detailseite/person-3895</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>Orange - Vaucluse, Frankreich (wh. 32, Boulevard de la Mergue, Orange -Vauculuse)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>32 boulevard de frankreich la mergue orange vaucluse vauculuse wh</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>Orange (Frankreich)</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>44.14</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>4.81</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>https://gedenkbuch.saarbruecken.de/gedenkbuch/personen_detailseite/person-3895</t>
         </is>
@@ -2760,444 +3420,619 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Orange - Vaucluse, Frankreich (wh. 32, Boulevard de la Mergue, Orange -Vauculuse)</t>
+          <t>Palästina</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>44.14</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>https://gedenkbuch.saarbruecken.de/gedenkbuch/personen_detailseite/person-3895</t>
+          <t>palästina</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>40.61</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>21.43</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1183</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Palästina</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>paris</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>48.85341</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2.3488</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2988507</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1183</t>
+          <t>https://www.wikidata.org/wiki/Q90</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>https://www.sommer-archive.com/english</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris, Frankreich</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>frankreich paris</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>48.85341</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>2.3488</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2988507</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q90</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>https://www.sommer-archive.com/english</t>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1183</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Paris, Frankreich</t>
+          <t>Paris, Montmartre Friedhof</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>48.85341</t>
+          <t>friedhof montmartre paris</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2.3488</t>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>48.8879</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2988507</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1183</t>
+          <t>2.32996</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6452785</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Paris, Montmartre Friedhof</t>
+          <t>Pompignan/Hte. Garonne Nähe Toulouse</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>48.8879</t>
+          <t>garonne nähe pompignanhte toulouse</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2.32996</t>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>43.81759</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/6452785</t>
+          <t>1.31286</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/11127093/chateau-de-pompignan.html</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q943312</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Pompignan/Hte. Garonne Nähe Toulouse</t>
+          <t>R 7, 24 (Strasse)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>43.81759</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>1.31286</t>
+          <t>24 7 r strasse</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/11127093/chateau-de-pompignan.html</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q943312</t>
+          <t>7.99</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>R 7, 24 (Strasse)</t>
+          <t>Ramat HaSharon, Israel</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>hasharon israel ramat</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>32.15934</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>34.8932</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/294760/hod-hasharon.html</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.wikidata.org/wiki/Q152379 </t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ramat HaSharon, Israel</t>
+          <t>Rexingen</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>32.15934</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>34.8932</t>
+          <t>rexingen</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>48.43931</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/294760/hod-hasharon.html</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.wikidata.org/wiki/Q152379 </t>
+          <t>8.65023</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2847721</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
+          <t>https://www.wikidata.org/wiki/Q2147112</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Rexingen</t>
+          <t>Schlesien</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>48.43931</t>
+          <t>schlesien</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>8.65023</t>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>51</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2847721</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2147112</t>
+          <t>alte_heimat</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Schlesien</t>
+          <t>Sussex</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>sussex</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>alte_heimat</t>
+          <t>50.9471026998</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-0.141372694746</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q23346</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sussex</t>
+          <t>Synagoge am Börneplatz, Frankfurt/M</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>50.9471026998</t>
+          <t>am börneplatz frankfurtm synagoge</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>-0.141372694746</t>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>50.11035</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>8.67185</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q23346</t>
+          <t>Synagoge,alte_heimat</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6553153/frankfurt-am-main.html</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1794</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Synagoge am Börneplatz, Frankfurt/M</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>50.11035</t>
+          <t>syracuse</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>8.67185</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Synagoge,alte_heimat</t>
+          <t>43.04812</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/6553153/frankfurt-am-main.html</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1794</t>
+          <t>-76.14742</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/5140405</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q128069</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>https://obits.syracuse.com/us/obituaries/syracuse/name/hannah-oppenheimer-obituary?id=39044601</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://ballweg.store.helloflowers.com/obituaries/Hannah-Oppenheimer/#!/TributeWall</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Südfrankreich</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>43.04812</t>
+          <t>südfrankreich</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>-76.14742</t>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>46.56</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/5140405</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q128069</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>https://obits.syracuse.com/us/obituaries/syracuse/name/hannah-oppenheimer-obituary?id=39044601</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>https://ballweg.store.helloflowers.com/obituaries/Hannah-Oppenheimer/#!/TributeWall</t>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://gedenkbuch.saarbruecken.de/gedenkbuch/personen_detailseite/person-3855</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>Südfrankreich  (Toulouse?)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>südfrankreich toulouse</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
           <t>Südfrankreich</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>46.56</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>https://gedenkbuch.saarbruecken.de/gedenkbuch/personen_detailseite/person-3855</t>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>45.24</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>3.5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Südfrankreich  (Toulouse?)</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>45.24</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>3.5</t>
+          <t>aviv tel</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>32.08088</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>34.78057</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>Tel Aviv (Ben-Jehuda-Straße)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>aviv benjehudastraße tel</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
           <t>Tel Aviv</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>32.08088</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>34.78057</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/293397</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q33935</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Tel Aviv (Ben-Jehuda-Straße)</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>32.08088</t>
+          <t>toulouse</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>34.78057</t>
+          <t>Südfrankreich</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>43.60426</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/293397</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q33935</t>
+          <t>1.44367</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>Toulouse (bei Fernayrol, 5 rue Bayard)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5 bayard bei fernayrol rue toulouse</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>43.60426</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>1.44367</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2972315</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q7880</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
         </is>
@@ -3206,372 +4041,1475 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Toulouse (bei Fernayrol, 5 rue Bayard)</t>
+          <t>Tynemouth</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>43.60426</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>1.44367</t>
+          <t>tynemouth</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>55.01788</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2972315</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q7880</t>
+          <t>-1.42559</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2635269</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://gedenkbuch.saarbruecken.de/en/memorial_book/person_details/person-1182</t>
+          <t>https://www.wikidata.org/wiki/Q1755020</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tynemouth</t>
+          <t>Uehlfeld a/Aisch</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>55.01788</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>-1.42559</t>
+          <t>aaisch uehlfeld</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>49.67085</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2635269</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1755020</t>
+          <t>10.72017</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2820334</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q33509937</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Uehlfeld a/Aisch</t>
+          <t>Umgebung von Nyons</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>49.67085</t>
+          <t>nyons umgebung von</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>10.72017</t>
+          <t>Nyons</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>47.68</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2820334</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q33509937</t>
+          <t>6.01</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Umgebung von Nyons</t>
+          <t>Upstate University Hospital</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>hospital university upstate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t xml:space="preserve">Syracuse </t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>43.04187</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-76.13981</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/7180645</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q30254105</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Upstate University Hospital</t>
+          <t>Weißensee</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>43.04187</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>-76.13981</t>
+          <t>weißensee</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>52.544722222222</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/7180645</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q30254105</t>
+          <t>13.458333333333</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q675174</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Weißensee</t>
+          <t>Wien</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>52.544722222222</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>13.458333333333</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q675174</t>
+          <t>wien</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>48.20849</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>16.37208</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2761369</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q702289</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Alice_Urbach</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Wien</t>
+          <t>Windermere</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>48.20849</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>16.37208</t>
+          <t>windermere</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>54.37296</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2761369</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q702289</t>
-        </is>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>https://de.wikipedia.org/wiki/Alice_Urbach</t>
+          <t>-2.93438</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2633852</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q390370</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/OldBowness/posts/3431692513769892/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Windermere</t>
+          <t>York</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>54.37296</t>
+          <t>york</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>-2.93438</t>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>53.96</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2633852</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q390370</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/OldBowness/posts/3431692513769892/</t>
+          <t>-1.08</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>53.96</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>-1.08</t>
+          <t>zürich</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>47.36667</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>8.55</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2657896</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>hôtel Monnier, puis s’installent place de la République, Nyons, Südfrankreich (bei Avignon)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>47.36667</t>
+          <t>avignon bei de hôtel la monnier nyons place puis république sinstallent südfrankreich</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>Avignon (Südfrankreich)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>44.36082</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2657896</t>
+          <t>5.14052</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2989819</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q209810</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/groups/nyonsaujourdhui/posts/1239122821734315/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>hôtel Monnier, puis s’installent place de la République, Nyons, Südfrankreich (bei Avignon)</t>
+          <t>Ägypten/Irak/Iran</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>44.36082</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>5.14052</t>
+          <t>ägyptenirakiran</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>35.06</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2989819</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q209810</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/nyonsaujourdhui/posts/1239122821734315/</t>
+          <t>47.26</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ägypten/Irak/Iran</t>
+          <t>Ēmeq Yizrəʿēl</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>35.06</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>47.26</t>
+          <t>yizrəʿēl ēmeq</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>32.60417</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>35.23639</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/293165/jezreel-valley.html</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q763829</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ēmeq Yizrəʿēl</t>
+          <t>Ägypten</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>32.60417</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>35.23639</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/293165/jezreel-valley.html</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q763829</t>
+          <t>ägypten</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/357994/arab-republic-of-egypt.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ägypten</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/357994/arab-republic-of-egypt.html</t>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>irak</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/99237/republic-of-iraq.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/99237/republic-of-iraq.html</t>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>iran</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/130758/islamic-republic-of-iran.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/130758/islamic-republic-of-iran.html</t>
+          <t>Breidenbach</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>breidenbach</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Frankfurt/MJeschiwa</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>frankfurtmjeschiwa</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Gieen</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>gieen</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Gießen &gt; Geburtshaus</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>geburtshaus gießen</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Gießen</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Gießen Antisemitismus</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>antisemitismus gießen</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Gießen</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Gießen Schule</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>gießen schule</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Gießen</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Gießenjüdische Jugendgruppen</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>gießenjüdische jugendgruppen</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Hindenburg</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>hindenburg</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Kehl</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>kehl</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Marburg</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>marburg</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sennfeld</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>sennfeld</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Rhein</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>rhein</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Rheinha</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>rheinha</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Ghettohaus</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ghettohaus</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Emek</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>emek</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Ein Gev</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ein gev</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Ha'Ogen</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>haogen</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Haifa Bay</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>bay haifa</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Haifa</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Haifa Universität Haifa</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>haifa universität</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Haifa</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Kibbuz</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>kibbuz</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Kibbuz &gt; Kvutzat Rodges</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>kibbuz kvutzat rodges</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Kibbuz Rodges</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Kibbuz &gt; Tirat Tzvi</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>kibbuz tirat tzvi</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Kibbuz</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Kibbuz &gt; Tirat Zvi</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>kibbuz tirat zvi</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Kibbuz</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Kibbuz Ha'Ogen</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>haogen kibbuz</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ha'Ogen</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Kibbuz Rodges</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>kibbuz rodges</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Kibbuz</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Kibbuz in der Nähe von Akko</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>akko der in kibbuz nähe von</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Kibbuz</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Kirjat Bialik</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>bialik kirjat</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Kirjat Bialik &gt; Beit Katz</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>beit bialik katz kirjat</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Kirjat Bialik</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Nahalat Yehuda</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>nahalat yehuda</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Palstina  Israel</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>israel palstina</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Petah Tikva</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>petah tikva</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Rodges</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>rodges</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Tirat Tsvi</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>tirat tsvi</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Rischon le</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>le rischon</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>schweiz</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ukraine</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Theresienstadt</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>theresienstadt</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Elternhaus</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>elternhaus</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Fabrik i/ in der Nähe von Haifa</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>der fabrik haifa i in nähe von</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Haifa</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Wohnung Löberstraße 20</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>20 löberstraße wohnung</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Löberstraße 20</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Wohnung/Wohnort</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>wohnungwohnort</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Pardesim</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>pardesim</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Alte Heimat Schule</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>alte heimat schule</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>alte Heimat</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>alte Heimat</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>alte heimat</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>neue Heimat</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>heimat neue</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Neue Heimat vom Verein der ehemaligen Gießener</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>der ehemaligen gießener heimat neue verein vom</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>neue Heimat</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Città/regioni tedesche, austriache, ceche</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>austriache ceche cittàregioni tedesche</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Berlino</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>berlino</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Palestina / Israele – luoghi</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>israele luoghi palestina</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Europa – altri paesi e luoghi</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>altri e europa luoghi paesi</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Berlino – quartieri e luoghi</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>berlino e luoghi quartieri</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Berlino</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>GO</t>
         </is>
       </c>
     </row>

--- a/notebook/locations.xlsx
+++ b/notebook/locations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V176"/>
+  <dimension ref="A1:V246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,6 +1128,11 @@
           <t>11.24923</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>https://www.geonames.org/8644023</t>
@@ -1196,12 +1201,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Deutsches Reich</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>deutschland</t>
+          <t>deutsches reich</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1300,6 +1305,11 @@
           <t>-4.9680331</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2069,6 +2079,11 @@
           <t>8.69079</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2907911</t>
@@ -2093,7 +2108,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Deutsches Reich</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2724,6 +2739,11 @@
           <t>12.67942</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>https://www.geonames.org/3176589</t>
@@ -3706,7 +3726,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Deutsches Reich</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3926,6 +3946,11 @@
           <t>34.78057</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5510,6 +5535,1241 @@
       <c r="F176" t="inlineStr">
         <is>
           <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Charité</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>charité</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Adlon</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>adlon</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Ahava</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>ahava</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Alexanderplatz</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>alexanderplatz</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Alt-Moabit</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>altmoabit</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Bahnhof Zoo</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>bahnhof zoo</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Blindenwerkstatt Otto Weidt</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>blindenwerkstatt otto weidt</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Charlottenburg</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>charlottenburg</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Finanzamt</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>finanzamt</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Friedrichswerdersche Gymnasium</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>friedrichswerdersche gymnasium</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Friedrichshain</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>friedrichshain</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Französisches Gymnasium</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>französisches gymnasium</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Grunewald</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>grunewald</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Gymnasium zum Grauen Kloster</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>grauen gymnasium kloster zum</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Borsigsteg</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>borsigsteg</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Flensburgerstr.</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>flensburgerstr</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Lessingbrücke</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>lessingbrücke</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Stromstraße</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>stromstraße</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Bundesratufer</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>bundesratufer</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Krankenhaus Moabit</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>krankenhaus moabit</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Jugendalija-Büro</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>jugendalijabüro</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Luckenwalde bei Berlin</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>bei berlin luckenwalde</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Münchner Straße</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>münchner straße</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Neue Königstraße</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>königstraße neue</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Oranienburg</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>oranienburg</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Ost-Berlin</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ostberlin</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Pankow</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>pankow</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Pfaueninsel</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>pfaueninsel</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Rykestraße (+)</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>rykestraße</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Schöneberg (+)</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>schöneberg</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Schönhauser Allee</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>allee schönhauser</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Sophien Realgymnasium</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>realgymnasium sophien</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Realgymnasium</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Staatsbibliothek</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>staatsbibliothek</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Tiergarten</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>tiergarten</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Richardstraße</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>richardstraße</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Zoologischer Garten</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>garten zoologischer</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Wannsee</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>wannsee</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Wittenbergplatz</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>wittenbergplatz</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>freiburg</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Volksschule (Pestalozzi)</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>pestalozzi volksschule</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Realgymnasium</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>realgymnasium</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>hamburg</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Hachscharazentrum</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>hachscharazentrum</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Königsberg</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>königsberg</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Gut Winkel</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>gut winkel</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Kreuzburg</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>kreuzburg</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Kreis Oppeln</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>kreis oppeln</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Breslau</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>breslau</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Tempel</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>tempel</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>III. Bezirk</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>bezirk iii</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Bet Sche'an</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>bet schean</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Ben Shemen</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ben shemen</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Hadassa</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>hadassa</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Deutsche DIakonissenhospital</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>deutsche diakonissenhospital</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Ramat haScharon (+)</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>hascharon ramat</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Raʿanana</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>raʿanana</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Rishon LeZion</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>lezion rishon</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Ahawa</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>ahawa</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Sde Warburg</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>sde warburg</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Polen</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>polen</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>bern</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Prag</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>prag</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>budapest</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Russland</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>russland</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Österreich</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>österreich</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Palästina – Israel</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>israel palästina</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Tschechoslowakei</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>tschechoslowakei</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Ungarn</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ungarn</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Flüsse</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>flüsse</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>deutschland</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>reise_zurueck</t>
         </is>
       </c>
     </row>

--- a/notebook/locations.xlsx
+++ b/notebook/locations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V246"/>
+  <dimension ref="A1:V247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6773,6 +6773,18 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
